--- a/artfynd/A 58954-2022 artfynd.xlsx
+++ b/artfynd/A 58954-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114972380</v>
+        <v>114972393</v>
       </c>
       <c r="B2" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>334417</v>
+        <v>334380</v>
       </c>
       <c r="R2" t="n">
-        <v>6418982</v>
+        <v>6418901</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114972385</v>
+        <v>114972394</v>
       </c>
       <c r="B3" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>334434</v>
+        <v>334374</v>
       </c>
       <c r="R3" t="n">
-        <v>6419189</v>
+        <v>6418924</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114972388</v>
+        <v>114972380</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>334427</v>
+        <v>334417</v>
       </c>
       <c r="R4" t="n">
-        <v>6419146</v>
+        <v>6418982</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +940,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-03-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gammalt hackspår</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,12 +969,7 @@
         <v>114972381</v>
       </c>
       <c r="B5" t="n">
-        <v>94069</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1085,6 +1060,496 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114972384</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>334422</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6419170</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114972385</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96348</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>334434</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6419189</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>114972392</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>334443</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6418872</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>114972387</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>334427</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6418862</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>114972388</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Alefjäll, Vg</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>334427</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6419146</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Gammalt hackspår</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58954-2022 artfynd.xlsx
+++ b/artfynd/A 58954-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972393</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972380</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972381</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972384</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972385</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972392</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972387</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,8 +1595,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114972388</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>